--- a/data/trans_bre/P3A_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 6,53</t>
+          <t>-6,05; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 2,18</t>
+          <t>-12,55; 2,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -0,74</t>
+          <t>-14,56; -0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 0,41</t>
+          <t>-10,87; 0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 25,95</t>
+          <t>-20,56; 27,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 6,51</t>
+          <t>-32,3; 5,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,1; -1,85</t>
+          <t>-32,69; -2,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 1,72</t>
+          <t>-26,46; 0,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 1,32</t>
+          <t>-10,87; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -6,08</t>
+          <t>-19,42; -5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,51; -7,15</t>
+          <t>-21,69; -6,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -0,11</t>
+          <t>-12,08; -0,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 5,04</t>
+          <t>-35,31; 9,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -18,67</t>
+          <t>-49,84; -16,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -16,39</t>
+          <t>-41,54; -14,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 0,08</t>
+          <t>-32,27; -1,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,35; -6,16</t>
+          <t>-18,52; -5,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -5,58</t>
+          <t>-17,66; -5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -2,07</t>
+          <t>-18,89; -2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 20,25</t>
+          <t>-9,58; 21,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -28,48</t>
+          <t>-69,76; -24,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,38; -17,97</t>
+          <t>-52,91; -17,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,87; -4,39</t>
+          <t>-47,05; -5,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 257,97</t>
+          <t>-29,94; 253,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -3,78</t>
+          <t>-10,73; -3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -4,54</t>
+          <t>-11,9; -3,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -10,67</t>
+          <t>-18,23; -10,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -1,03</t>
+          <t>-19,37; -1,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,67; -19,87</t>
+          <t>-48,6; -19,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -17,32</t>
+          <t>-42,45; -13,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; -31,28</t>
+          <t>-49,56; -31,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,89; -3,66</t>
+          <t>-62,25; -4,35</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -4,64</t>
+          <t>-13,98; -4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -8,42</t>
+          <t>-17,34; -8,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -5,89</t>
+          <t>-13,92; -5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -1,01</t>
+          <t>-12,39; -0,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,45; -33,19</t>
+          <t>-68,09; -31,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,55; -39,73</t>
+          <t>-64,54; -37,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -27,52</t>
+          <t>-54,07; -25,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,31; -5,16</t>
+          <t>-45,92; -4,79</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,65</t>
+          <t>3,29; 6,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,1</t>
+          <t>4,81; 8,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,51</t>
+          <t>6,16; 10,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,72</t>
+          <t>2,0; 8,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,62; —</t>
+          <t>118,44; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>181,36; 2703,63</t>
+          <t>182,71; 2560,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,63; 1070,27</t>
+          <t>10,95; 1071,87</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -7,14</t>
+          <t>-10,75; -7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -10,54</t>
+          <t>-14,55; -10,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,2; -11,95</t>
+          <t>-16,01; -11,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -0,93</t>
+          <t>-10,89; -0,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-48,91; -35,92</t>
+          <t>-48,68; -35,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-51,01; -39,99</t>
+          <t>-51,3; -40,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,7; -37,98</t>
+          <t>-47,38; -37,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,87; -7,35</t>
+          <t>-37,75; -6,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,31</t>
+          <t>-6,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>-15,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 7,04</t>
+          <t>-6,62; 7,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 2,12</t>
+          <t>-12,01; 1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -0,98</t>
+          <t>-14,89; -0,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 0,2</t>
+          <t>-11,53; -0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 27,94</t>
+          <t>-21,16; 29,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 5,9</t>
+          <t>-32,09; 5,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -2,21</t>
+          <t>-34,24; -0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 0,68</t>
+          <t>-27,53; -2,35</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>-7,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-17,75%</t>
+          <t>-21,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 2,13</t>
+          <t>-11,71; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,42; -5,59</t>
+          <t>-20,39; -5,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -6,81</t>
+          <t>-21,18; -7,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -0,61</t>
+          <t>-13,5; -1,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 9,14</t>
+          <t>-36,7; 7,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,84; -16,84</t>
+          <t>-50,26; -17,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -14,59</t>
+          <t>-41,79; -17,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,27; -1,9</t>
+          <t>-35,12; -4,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>-7,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>-24,3%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -5,97</t>
+          <t>-18,17; -5,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -5,15</t>
+          <t>-17,38; -5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -2,04</t>
+          <t>-18,23; -1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 21,39</t>
+          <t>-14,28; -0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,76; -24,62</t>
+          <t>-68,87; -25,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,91; -17,27</t>
+          <t>-51,73; -17,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -5,46</t>
+          <t>-45,89; -3,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 253,6</t>
+          <t>-40,79; -1,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,35</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-28,13%</t>
+          <t>-11,1%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -3,9</t>
+          <t>-10,48; -3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -3,44</t>
+          <t>-12,73; -4,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -10,46</t>
+          <t>-18,55; -9,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -1,25</t>
+          <t>-7,3; 0,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,6; -19,33</t>
+          <t>-48,84; -19,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,45; -13,95</t>
+          <t>-44,44; -17,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,56; -31,63</t>
+          <t>-50,36; -30,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,25; -4,35</t>
+          <t>-23,13; 1,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,25%</t>
+          <t>-13,41%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,98; -4,44</t>
+          <t>-14,0; -5,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -8,14</t>
+          <t>-17,73; -8,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -5,22</t>
+          <t>-13,96; -5,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -0,97</t>
+          <t>-7,35; 1,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,09; -31,92</t>
+          <t>-69,09; -33,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,54; -37,92</t>
+          <t>-65,53; -39,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-54,07; -25,17</t>
+          <t>-53,93; -25,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,92; -4,79</t>
+          <t>-29,13; 8,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>239,1%</t>
+          <t>190,0%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,88</t>
+          <t>3,2; 6,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,32</t>
+          <t>4,67; 8,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,53</t>
+          <t>5,79; 10,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,97</t>
+          <t>1,98; 8,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118,44; —</t>
+          <t>93,46; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>182,71; 2560,0</t>
+          <t>162,38; 2430,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 1071,87</t>
+          <t>21,16; 779,46</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,92</t>
+          <t>-7,68</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-25,59%</t>
+          <t>-26,41%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -7,02</t>
+          <t>-10,66; -7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -10,68</t>
+          <t>-14,57; -10,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -11,88</t>
+          <t>-16,22; -11,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -0,85</t>
+          <t>-9,6; -5,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-48,68; -35,2</t>
+          <t>-48,68; -35,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -40,32</t>
+          <t>-51,0; -39,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,38; -37,87</t>
+          <t>-48,03; -37,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -6,34</t>
+          <t>-32,0; -20,85</t>
         </is>
       </c>
     </row>
